--- a/artfynd/S 547-2025 artfynd.xlsx
+++ b/artfynd/S 547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98706846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387179</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387672</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347570</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068609</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362284</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362285</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386246</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386247</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387199</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387247</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387248</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2181,6 +2256,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387249</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068790</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068807</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068808</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068809</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2716,6 +2816,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068810</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068811</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068812</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3037,6 +3152,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068813</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3144,6 +3264,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068814</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3241,6 +3366,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127362267</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3348,6 +3478,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068571</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3455,6 +3590,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347521</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3552,6 +3692,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387191</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3649,6 +3794,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387238</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3756,6 +3906,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068643</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,6 +4016,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387674</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3968,6 +4128,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347870</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4075,6 +4240,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347682</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4172,6 +4342,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387739</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4269,6 +4444,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387184</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4366,6 +4546,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387677</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4472,6 +4657,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106157917</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4579,6 +4769,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068589</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4686,6 +4881,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307350</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4793,6 +4993,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307259</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4900,6 +5105,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307303</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5007,6 +5217,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307335</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5114,6 +5329,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307406</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5211,6 +5431,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386243</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5308,6 +5533,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386244</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5415,6 +5645,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068815</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5522,6 +5757,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068816</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5629,6 +5869,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068817</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5736,6 +5981,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068818</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5843,6 +6093,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068819</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5950,6 +6205,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068820</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6057,6 +6317,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307135</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6169,6 +6434,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307397</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6285,6 +6555,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124307165</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6382,6 +6657,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387738</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6479,8 +6759,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387734</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>